--- a/APPT/data/output/Final Production Plan 2026-01-14.xlsx
+++ b/APPT/data/output/Final Production Plan 2026-01-14.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="286">
   <si>
     <t>Batch ID</t>
   </si>
@@ -119,10 +119,13 @@
     <t>REP45</t>
   </si>
   <si>
+    <t>REP46</t>
+  </si>
+  <si>
     <t>B021</t>
   </si>
   <si>
-    <t>REP46</t>
+    <t>REP47</t>
   </si>
   <si>
     <t>B022</t>
@@ -131,15 +134,15 @@
     <t>B016</t>
   </si>
   <si>
-    <t>REP47</t>
-  </si>
-  <si>
     <t>B023</t>
   </si>
   <si>
     <t>B041</t>
   </si>
   <si>
+    <t>REP48</t>
+  </si>
+  <si>
     <t>B017</t>
   </si>
   <si>
@@ -149,27 +152,27 @@
     <t>B025</t>
   </si>
   <si>
-    <t>REP48</t>
-  </si>
-  <si>
     <t>B026</t>
   </si>
   <si>
     <t>B027</t>
   </si>
   <si>
+    <t>REP49</t>
+  </si>
+  <si>
     <t>B029</t>
   </si>
   <si>
-    <t>REP49</t>
-  </si>
-  <si>
     <t>B030</t>
   </si>
   <si>
     <t>B031</t>
   </si>
   <si>
+    <t>REP50</t>
+  </si>
+  <si>
     <t>B032</t>
   </si>
   <si>
@@ -314,37 +317,37 @@
     <t>6T</t>
   </si>
   <si>
+    <t>TK#_23_#</t>
+  </si>
+  <si>
+    <t>TK#_14_#</t>
+  </si>
+  <si>
+    <t>TK#_16_#</t>
+  </si>
+  <si>
+    <t>NO_TANK</t>
+  </si>
+  <si>
+    <t>TK#_53_#</t>
+  </si>
+  <si>
+    <t>TK#_15_#</t>
+  </si>
+  <si>
+    <t>TK#_58_#</t>
+  </si>
+  <si>
+    <t>TK#_57_#</t>
+  </si>
+  <si>
+    <t>TK#_9_#</t>
+  </si>
+  <si>
+    <t>TK#_56_#</t>
+  </si>
+  <si>
     <t>TK#_24_#</t>
-  </si>
-  <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>NO_TANK</t>
-  </si>
-  <si>
-    <t>TK#_58_#</t>
-  </si>
-  <si>
-    <t>TK#_57_#</t>
-  </si>
-  <si>
-    <t>TK#_9_#</t>
-  </si>
-  <si>
-    <t>TK#_23_#</t>
-  </si>
-  <si>
-    <t>TK#_53_#</t>
-  </si>
-  <si>
-    <t>TK#_56_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
   </si>
   <si>
     <t>TK#_12_#</t>
@@ -1231,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1265,13 +1268,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2">
         <v>46036.16041666667</v>
@@ -1280,10 +1283,10 @@
         <v>46036.22291666667</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1291,13 +1294,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="2">
         <v>46036.22291666667</v>
@@ -1306,10 +1309,10 @@
         <v>46036.28541666667</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1317,13 +1320,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" s="2">
         <v>46036.35902777778</v>
@@ -1332,10 +1335,10 @@
         <v>46036.42152777778</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1343,13 +1346,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2">
         <v>46036.42152777778</v>
@@ -1358,10 +1361,10 @@
         <v>46036.48402777778</v>
       </c>
       <c r="G5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1369,13 +1372,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2">
         <v>46036.59027777778</v>
@@ -1384,10 +1387,10 @@
         <v>46036.65277777778</v>
       </c>
       <c r="G6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1395,13 +1398,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2">
         <v>46036.67708333334</v>
@@ -1410,10 +1413,10 @@
         <v>46036.73958333334</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1421,13 +1424,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="2">
         <v>46036.77361111111</v>
@@ -1439,7 +1442,7 @@
         <v>102</v>
       </c>
       <c r="H8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1447,13 +1450,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" s="2">
         <v>46036.89027777778</v>
@@ -1462,10 +1465,10 @@
         <v>46036.95277777778</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1473,13 +1476,13 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" s="2">
         <v>46036.95763888889</v>
@@ -1488,10 +1491,10 @@
         <v>46037.02013888889</v>
       </c>
       <c r="G10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1499,13 +1502,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E11" s="2">
         <v>46037.07847222222</v>
@@ -1514,10 +1517,10 @@
         <v>46037.14097222222</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1525,13 +1528,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" s="2">
         <v>46037.14097222222</v>
@@ -1540,10 +1543,10 @@
         <v>46037.20347222222</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1551,13 +1554,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" s="2">
         <v>46037.325</v>
@@ -1566,10 +1569,10 @@
         <v>46037.3875</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1577,13 +1580,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E14" s="2">
         <v>46037.40277777778</v>
@@ -1592,10 +1595,10 @@
         <v>46037.46875</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1603,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2">
         <v>46037.46875</v>
@@ -1618,10 +1621,10 @@
         <v>46037.53125</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1629,13 +1632,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" s="2">
         <v>46037.53125</v>
@@ -1644,10 +1647,10 @@
         <v>46037.59375</v>
       </c>
       <c r="G16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1655,13 +1658,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" s="2">
         <v>46037.61597222222</v>
@@ -1670,10 +1673,10 @@
         <v>46037.68194444444</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1681,13 +1684,13 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2">
         <v>46037.68194444444</v>
@@ -1696,10 +1699,10 @@
         <v>46037.74444444444</v>
       </c>
       <c r="G18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1707,13 +1710,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" s="2">
         <v>46037.74444444444</v>
@@ -1722,10 +1725,10 @@
         <v>46037.80694444444</v>
       </c>
       <c r="G19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1733,13 +1736,13 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20" s="2">
         <v>46037.87638888889</v>
@@ -1748,10 +1751,10 @@
         <v>46037.93888888889</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1759,13 +1762,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2">
         <v>46035.2625</v>
@@ -1774,10 +1777,10 @@
         <v>46035.3875</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1785,13 +1788,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2">
         <v>46035.45</v>
@@ -1800,10 +1803,10 @@
         <v>46035.575</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1811,25 +1814,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2">
-        <v>46035.675</v>
+        <v>46035.65347222222</v>
       </c>
       <c r="F23" s="2">
-        <v>46035.8</v>
+        <v>46035.77847222222</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1837,25 +1840,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" s="2">
-        <v>46035.84166666667</v>
+        <v>46035.82013888889</v>
       </c>
       <c r="F24" s="2">
-        <v>46035.90416666667</v>
+        <v>46035.88263888889</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1863,25 +1866,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2">
-        <v>46035.93888888889</v>
+        <v>46035.91736111111</v>
       </c>
       <c r="F25" s="2">
-        <v>46036.06388888889</v>
+        <v>46036.04236111111</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1889,25 +1892,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2">
-        <v>46036.10555555556</v>
+        <v>46036.08402777778</v>
       </c>
       <c r="F26" s="2">
-        <v>46036.23055555556</v>
+        <v>46036.20902777778</v>
       </c>
       <c r="G26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1915,25 +1918,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" s="2">
-        <v>46036.23055555556</v>
+        <v>46036.20902777778</v>
       </c>
       <c r="F27" s="2">
-        <v>46036.35555555556</v>
+        <v>46036.33402777778</v>
       </c>
       <c r="G27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1947,19 +1950,19 @@
         <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2">
-        <v>46036.36944444444</v>
+        <v>46036.33402777778</v>
       </c>
       <c r="F28" s="2">
-        <v>46036.43194444444</v>
+        <v>46036.45902777778</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1967,25 +1970,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E29" s="2">
-        <v>46036.44583333333</v>
+        <v>46036.47291666667</v>
       </c>
       <c r="F29" s="2">
-        <v>46036.57083333333</v>
+        <v>46036.53541666667</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1993,25 +1996,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2">
-        <v>46036.58472222222</v>
+        <v>46036.54930555556</v>
       </c>
       <c r="F30" s="2">
-        <v>46036.64722222222</v>
+        <v>46036.67430555556</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2019,22 +2022,22 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E31" s="2">
-        <v>46036.66111111111</v>
+        <v>46036.68819444445</v>
       </c>
       <c r="F31" s="2">
-        <v>46036.72361111111</v>
+        <v>46036.75069444445</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" t="s">
         <v>112</v>
@@ -2045,22 +2048,22 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E32" s="2">
-        <v>46036.7375</v>
+        <v>46036.76458333333</v>
       </c>
       <c r="F32" s="2">
-        <v>46036.8625</v>
+        <v>46036.82708333333</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
         <v>113</v>
@@ -2071,25 +2074,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" s="2">
-        <v>46036.87638888889</v>
+        <v>46036.84097222222</v>
       </c>
       <c r="F33" s="2">
-        <v>46036.93541666667</v>
+        <v>46036.9</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2097,25 +2100,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E34" s="2">
-        <v>46036.97013888889</v>
+        <v>46036.93472222222</v>
       </c>
       <c r="F34" s="2">
-        <v>46037.03263888889</v>
+        <v>46036.99722222222</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2123,25 +2126,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E35" s="2">
-        <v>46037.07430555556</v>
+        <v>46037.03888888889</v>
       </c>
       <c r="F35" s="2">
-        <v>46037.13680555556</v>
+        <v>46037.16388888889</v>
       </c>
       <c r="G35" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2149,25 +2152,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36" s="2">
-        <v>46037.17152777778</v>
+        <v>46037.17777777778</v>
       </c>
       <c r="F36" s="2">
-        <v>46037.29652777778</v>
+        <v>46037.24027777778</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2175,25 +2178,25 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E37" s="2">
-        <v>46037.33819444444</v>
+        <v>46037.275</v>
       </c>
       <c r="F37" s="2">
-        <v>46037.39722222222</v>
+        <v>46037.4</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2201,25 +2204,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E38" s="2">
-        <v>46037.41111111111</v>
+        <v>46037.44166666667</v>
       </c>
       <c r="F38" s="2">
-        <v>46037.53611111111</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="G38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2227,25 +2230,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39" s="2">
-        <v>46037.55</v>
+        <v>46037.51458333333</v>
       </c>
       <c r="F39" s="2">
-        <v>46037.6125</v>
+        <v>46037.57708333333</v>
       </c>
       <c r="G39" t="s">
         <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2253,25 +2256,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E40" s="2">
-        <v>46037.6125</v>
+        <v>46037.57708333333</v>
       </c>
       <c r="F40" s="2">
-        <v>46037.675</v>
+        <v>46037.63958333333</v>
       </c>
       <c r="G40" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2279,25 +2282,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="2">
-        <v>46037.79236111111</v>
+        <v>46037.65347222222</v>
       </c>
       <c r="F41" s="2">
-        <v>46037.85486111111</v>
+        <v>46037.77847222222</v>
       </c>
       <c r="G41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2305,22 +2308,22 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2">
-        <v>46037.875</v>
+        <v>46037.79236111111</v>
       </c>
       <c r="F42" s="2">
-        <v>46038</v>
+        <v>46037.85486111111</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H42" t="s">
         <v>113</v>
@@ -2331,25 +2334,25 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E43" s="2">
-        <v>46038.01388888889</v>
+        <v>46037.86111111111</v>
       </c>
       <c r="F43" s="2">
-        <v>46038.07638888889</v>
+        <v>46037.92361111111</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2357,25 +2360,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E44" s="2">
-        <v>46038.09027777778</v>
+        <v>46037.9375</v>
       </c>
       <c r="F44" s="2">
-        <v>46038.14930555555</v>
+        <v>46037.99652777778</v>
       </c>
       <c r="G44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2383,25 +2386,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E45" s="2">
-        <v>46038.14930555555</v>
+        <v>46038.01041666666</v>
       </c>
       <c r="F45" s="2">
-        <v>46038.20833333334</v>
+        <v>46038.13541666666</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2409,25 +2412,25 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
         <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46" s="2">
-        <v>46038.24305555555</v>
+        <v>46038.14930555555</v>
       </c>
       <c r="F46" s="2">
-        <v>46038.30555555555</v>
+        <v>46038.20833333334</v>
       </c>
       <c r="G46" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2435,25 +2438,25 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E47" s="2">
-        <v>46038.34722222222</v>
+        <v>46038.24305555555</v>
       </c>
       <c r="F47" s="2">
-        <v>46038.40625</v>
+        <v>46038.30555555555</v>
       </c>
       <c r="G47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H47" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2461,25 +2464,25 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E48" s="2">
-        <v>46038.42013888889</v>
+        <v>46038.34722222222</v>
       </c>
       <c r="F48" s="2">
-        <v>46038.48263888889</v>
+        <v>46038.40625</v>
       </c>
       <c r="G48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2487,25 +2490,25 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
         <v>95</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2">
-        <v>46038.49652777778</v>
+        <v>46038.42013888889</v>
       </c>
       <c r="F49" s="2">
-        <v>46038.55902777778</v>
+        <v>46038.48263888889</v>
       </c>
       <c r="G49" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H49" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2513,25 +2516,51 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
         <v>96</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E50" s="2">
+        <v>46038.49652777778</v>
+      </c>
+      <c r="F50" s="2">
+        <v>46038.55902777778</v>
+      </c>
+      <c r="G50" t="s">
+        <v>110</v>
+      </c>
+      <c r="H50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" s="2">
         <v>46038.57291666666</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F51" s="2">
         <v>46038.63194444445</v>
       </c>
-      <c r="G50" t="s">
-        <v>105</v>
-      </c>
-      <c r="H50" t="s">
-        <v>111</v>
+      <c r="G51" t="s">
+        <v>108</v>
+      </c>
+      <c r="H51" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2546,26 +2575,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -2573,7 +2602,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -2581,7 +2610,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -2589,7 +2618,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -2597,7 +2626,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -2605,7 +2634,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -2613,22 +2642,22 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -2636,7 +2665,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -2644,7 +2673,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -2652,7 +2681,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
@@ -2660,7 +2689,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -2668,7 +2697,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
@@ -2676,32 +2705,35 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -2709,7 +2741,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
@@ -2717,7 +2749,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
@@ -2725,7 +2757,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
@@ -2733,7 +2765,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
         <v>29</v>
@@ -2741,25 +2773,25 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
@@ -2767,7 +2799,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
@@ -2775,25 +2807,25 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
@@ -2801,7 +2833,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
@@ -2809,7 +2841,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
@@ -2817,7 +2849,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
@@ -2825,7 +2857,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
@@ -2833,25 +2865,25 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -2859,7 +2891,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -2867,7 +2899,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -2878,7 +2910,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -2889,7 +2921,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -2900,18 +2932,18 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -2922,7 +2954,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -2933,7 +2965,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
         <v>33</v>
@@ -2941,7 +2973,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
         <v>33</v>
@@ -2949,7 +2981,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
@@ -2957,15 +2989,15 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
@@ -2976,7 +3008,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -2987,7 +3019,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -2998,26 +3030,29 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
@@ -3028,7 +3063,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C62" t="s">
         <v>35</v>
@@ -3036,7 +3071,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" t="s">
         <v>35</v>
@@ -3044,28 +3079,28 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
@@ -3076,7 +3111,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -3087,7 +3122,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -3098,26 +3133,23 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
-      <c r="C71" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -3128,23 +3160,26 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
+      <c r="C73" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C75" t="s">
         <v>38</v>
@@ -3152,7 +3187,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -3163,7 +3198,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -3174,31 +3209,31 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B78" t="s">
         <v>14</v>
       </c>
-      <c r="C78" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="C80" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
@@ -3209,34 +3244,37 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
       </c>
-      <c r="C82" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B83" t="s">
         <v>15</v>
       </c>
+      <c r="C83" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B84" t="s">
         <v>16</v>
       </c>
+      <c r="C84" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B85" t="s">
         <v>16</v>
@@ -3247,36 +3285,36 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B86" t="s">
         <v>16</v>
       </c>
-      <c r="C86" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>203</v>
-      </c>
-      <c r="C87" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="C88" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="C89" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3287,7 +3325,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -3298,7 +3336,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -3309,15 +3347,18 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B93" t="s">
         <v>18</v>
       </c>
+      <c r="C93" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B94" t="s">
         <v>18</v>
@@ -3325,7 +3366,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
         <v>18</v>
@@ -3336,7 +3377,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s">
         <v>42</v>
@@ -3344,7 +3385,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C97" t="s">
         <v>42</v>
@@ -3352,44 +3393,44 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>214</v>
-      </c>
-      <c r="C98" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" t="s">
-        <v>42</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C100" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>217</v>
+        <v>218</v>
+      </c>
+      <c r="C101" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B102" t="s">
         <v>19</v>
       </c>
+      <c r="C102" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
@@ -3400,7 +3441,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
@@ -3411,7 +3452,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s">
         <v>43</v>
@@ -3419,29 +3460,23 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B106" t="s">
         <v>20</v>
       </c>
-      <c r="C106" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B107" t="s">
         <v>20</v>
       </c>
-      <c r="C107" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B108" t="s">
         <v>20</v>
@@ -3452,7 +3487,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
         <v>21</v>
@@ -3463,7 +3498,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B110" t="s">
         <v>21</v>
@@ -3474,26 +3509,29 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B111" t="s">
         <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B112" t="s">
         <v>22</v>
       </c>
+      <c r="C112" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B113" t="s">
         <v>22</v>
@@ -3504,26 +3542,26 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B114" t="s">
         <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C115" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B116" t="s">
         <v>23</v>
@@ -3534,69 +3572,81 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
       </c>
-      <c r="C117" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B118" t="s">
         <v>23</v>
       </c>
       <c r="C118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B119" t="s">
         <v>24</v>
       </c>
+      <c r="C119" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B120" t="s">
         <v>24</v>
       </c>
+      <c r="C120" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B121" t="s">
         <v>24</v>
       </c>
+      <c r="C121" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
         <v>25</v>
       </c>
+      <c r="C122" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B123" t="s">
         <v>25</v>
       </c>
+      <c r="C123" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B124" t="s">
         <v>25</v>
@@ -3604,327 +3654,327 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C125" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C127" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B129" t="s">
         <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B130" t="s">
         <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B131" t="s">
         <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C132" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C133" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C135" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C136" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="C138" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C140" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>257</v>
-      </c>
-      <c r="C141" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C142" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C146" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C147" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C148" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C152" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C153" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C155" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C156" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C157" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C158" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C159" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C160" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C162" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
